--- a/artfynd/A 55975-2025 artfynd.xlsx
+++ b/artfynd/A 55975-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -935,46 +935,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128069845</v>
+        <v>137092470</v>
       </c>
       <c r="B4" t="n">
-        <v>93392</v>
+        <v>96573</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6331651</v>
+        <v>2812</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kransmossa</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon melilotinus</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Quél.) Svantesson</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Österängsån, Dlr</t>
+          <t>Rättvik, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510130</v>
+        <v>510165</v>
       </c>
       <c r="R4" t="n">
-        <v>6751440</v>
+        <v>6751449</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,12 +1000,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,23 +1024,795 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Emma Billbäck</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Emma Billbäck</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137092470</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137092472</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99396</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Rättvik, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>510193</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6751483</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137092472</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137092473</v>
+      </c>
+      <c r="B6" t="n">
+        <v>108386</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Rättvik, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>510230</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6751456</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137092473</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137092474</v>
+      </c>
+      <c r="B7" t="n">
+        <v>108386</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rättvik, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>510248</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6751461</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137092474</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137092475</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99361</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Rättvik, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>510253</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6751477</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137092475</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137092468</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101571</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Rättvik, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>510212</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6751414</v>
+      </c>
+      <c r="S9" t="n">
+        <v>6</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137092468</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137092471</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101571</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Rättvik, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>510166</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6751448</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137092471</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128069845</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93392</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6331651</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellodon melilotinus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Quél.) Svantesson</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Österängsån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>510130</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6751440</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Emma Billbäck</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Emma Billbäck</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128069845</t>
         </is>
@@ -1039,6 +1823,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55975-2025 artfynd.xlsx
+++ b/artfynd/A 55975-2025 artfynd.xlsx
@@ -938,7 +938,7 @@
         <v>137092470</v>
       </c>
       <c r="B4" t="n">
-        <v>96573</v>
+        <v>96574</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>137092472</v>
       </c>
       <c r="B5" t="n">
-        <v>99396</v>
+        <v>99397</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>137092473</v>
       </c>
       <c r="B6" t="n">
-        <v>108386</v>
+        <v>108387</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>137092474</v>
       </c>
       <c r="B7" t="n">
-        <v>108386</v>
+        <v>108387</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>137092475</v>
       </c>
       <c r="B8" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>137092468</v>
       </c>
       <c r="B9" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>137092471</v>
       </c>
       <c r="B10" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 55975-2025 artfynd.xlsx
+++ b/artfynd/A 55975-2025 artfynd.xlsx
@@ -938,7 +938,7 @@
         <v>137092470</v>
       </c>
       <c r="B4" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>137092472</v>
       </c>
       <c r="B5" t="n">
-        <v>99397</v>
+        <v>99403</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>137092473</v>
       </c>
       <c r="B6" t="n">
-        <v>108387</v>
+        <v>108393</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>137092474</v>
       </c>
       <c r="B7" t="n">
-        <v>108387</v>
+        <v>108393</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>137092475</v>
       </c>
       <c r="B8" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>137092468</v>
       </c>
       <c r="B9" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>137092471</v>
       </c>
       <c r="B10" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 55975-2025 artfynd.xlsx
+++ b/artfynd/A 55975-2025 artfynd.xlsx
@@ -938,7 +938,7 @@
         <v>137092470</v>
       </c>
       <c r="B4" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>137092472</v>
       </c>
       <c r="B5" t="n">
-        <v>99403</v>
+        <v>99407</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>137092473</v>
       </c>
       <c r="B6" t="n">
-        <v>108393</v>
+        <v>108397</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>137092474</v>
       </c>
       <c r="B7" t="n">
-        <v>108393</v>
+        <v>108397</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>137092475</v>
       </c>
       <c r="B8" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>137092468</v>
       </c>
       <c r="B9" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>137092471</v>
       </c>
       <c r="B10" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 55975-2025 artfynd.xlsx
+++ b/artfynd/A 55975-2025 artfynd.xlsx
@@ -938,7 +938,7 @@
         <v>137092470</v>
       </c>
       <c r="B4" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>137092472</v>
       </c>
       <c r="B5" t="n">
-        <v>99407</v>
+        <v>99409</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>137092473</v>
       </c>
       <c r="B6" t="n">
-        <v>108397</v>
+        <v>108399</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>137092474</v>
       </c>
       <c r="B7" t="n">
-        <v>108397</v>
+        <v>108399</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>137092475</v>
       </c>
       <c r="B8" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>137092468</v>
       </c>
       <c r="B9" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>137092471</v>
       </c>
       <c r="B10" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 55975-2025 artfynd.xlsx
+++ b/artfynd/A 55975-2025 artfynd.xlsx
@@ -938,7 +938,7 @@
         <v>137092470</v>
       </c>
       <c r="B4" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>137092472</v>
       </c>
       <c r="B5" t="n">
-        <v>99409</v>
+        <v>99411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>137092473</v>
       </c>
       <c r="B6" t="n">
-        <v>108399</v>
+        <v>108401</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>137092474</v>
       </c>
       <c r="B7" t="n">
-        <v>108399</v>
+        <v>108401</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>137092475</v>
       </c>
       <c r="B8" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>137092468</v>
       </c>
       <c r="B9" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>137092471</v>
       </c>
       <c r="B10" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 55975-2025 artfynd.xlsx
+++ b/artfynd/A 55975-2025 artfynd.xlsx
@@ -938,7 +938,7 @@
         <v>137092470</v>
       </c>
       <c r="B4" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>137092472</v>
       </c>
       <c r="B5" t="n">
-        <v>99411</v>
+        <v>99424</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>137092473</v>
       </c>
       <c r="B6" t="n">
-        <v>108401</v>
+        <v>108414</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>137092474</v>
       </c>
       <c r="B7" t="n">
-        <v>108401</v>
+        <v>108414</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>137092475</v>
       </c>
       <c r="B8" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>137092468</v>
       </c>
       <c r="B9" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>137092471</v>
       </c>
       <c r="B10" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 55975-2025 artfynd.xlsx
+++ b/artfynd/A 55975-2025 artfynd.xlsx
@@ -938,7 +938,7 @@
         <v>137092470</v>
       </c>
       <c r="B4" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>137092472</v>
       </c>
       <c r="B5" t="n">
-        <v>99424</v>
+        <v>99426</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>137092473</v>
       </c>
       <c r="B6" t="n">
-        <v>108414</v>
+        <v>108416</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>137092474</v>
       </c>
       <c r="B7" t="n">
-        <v>108414</v>
+        <v>108416</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>137092475</v>
       </c>
       <c r="B8" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>137092468</v>
       </c>
       <c r="B9" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>137092471</v>
       </c>
       <c r="B10" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 55975-2025 artfynd.xlsx
+++ b/artfynd/A 55975-2025 artfynd.xlsx
@@ -938,7 +938,7 @@
         <v>137092470</v>
       </c>
       <c r="B4" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>137092472</v>
       </c>
       <c r="B5" t="n">
-        <v>99426</v>
+        <v>99429</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>137092473</v>
       </c>
       <c r="B6" t="n">
-        <v>108416</v>
+        <v>108421</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>137092474</v>
       </c>
       <c r="B7" t="n">
-        <v>108416</v>
+        <v>108421</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>137092475</v>
       </c>
       <c r="B8" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>137092468</v>
       </c>
       <c r="B9" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>137092471</v>
       </c>
       <c r="B10" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 55975-2025 artfynd.xlsx
+++ b/artfynd/A 55975-2025 artfynd.xlsx
@@ -938,7 +938,7 @@
         <v>137092470</v>
       </c>
       <c r="B4" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>137092472</v>
       </c>
       <c r="B5" t="n">
-        <v>99429</v>
+        <v>99439</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>137092473</v>
       </c>
       <c r="B6" t="n">
-        <v>108421</v>
+        <v>108442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>137092474</v>
       </c>
       <c r="B7" t="n">
-        <v>108421</v>
+        <v>108442</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>137092475</v>
       </c>
       <c r="B8" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>137092468</v>
       </c>
       <c r="B9" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>137092471</v>
       </c>
       <c r="B10" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 55975-2025 artfynd.xlsx
+++ b/artfynd/A 55975-2025 artfynd.xlsx
@@ -938,7 +938,7 @@
         <v>137092470</v>
       </c>
       <c r="B4" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>137092472</v>
       </c>
       <c r="B5" t="n">
-        <v>99439</v>
+        <v>99440</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>137092473</v>
       </c>
       <c r="B6" t="n">
-        <v>108442</v>
+        <v>108443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>137092474</v>
       </c>
       <c r="B7" t="n">
-        <v>108442</v>
+        <v>108443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>137092475</v>
       </c>
       <c r="B8" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>137092468</v>
       </c>
       <c r="B9" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>137092471</v>
       </c>
       <c r="B10" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 55975-2025 artfynd.xlsx
+++ b/artfynd/A 55975-2025 artfynd.xlsx
@@ -938,7 +938,7 @@
         <v>137092470</v>
       </c>
       <c r="B4" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>137092472</v>
       </c>
       <c r="B5" t="n">
-        <v>99440</v>
+        <v>99445</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>137092473</v>
       </c>
       <c r="B6" t="n">
-        <v>108443</v>
+        <v>108448</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>137092474</v>
       </c>
       <c r="B7" t="n">
-        <v>108443</v>
+        <v>108448</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>137092475</v>
       </c>
       <c r="B8" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>137092468</v>
       </c>
       <c r="B9" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>137092471</v>
       </c>
       <c r="B10" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 55975-2025 artfynd.xlsx
+++ b/artfynd/A 55975-2025 artfynd.xlsx
@@ -938,7 +938,7 @@
         <v>137092470</v>
       </c>
       <c r="B4" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>137092472</v>
       </c>
       <c r="B5" t="n">
-        <v>99445</v>
+        <v>99447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>137092473</v>
       </c>
       <c r="B6" t="n">
-        <v>108448</v>
+        <v>108451</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>137092474</v>
       </c>
       <c r="B7" t="n">
-        <v>108448</v>
+        <v>108451</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>137092475</v>
       </c>
       <c r="B8" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>137092468</v>
       </c>
       <c r="B9" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>137092471</v>
       </c>
       <c r="B10" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 55975-2025 artfynd.xlsx
+++ b/artfynd/A 55975-2025 artfynd.xlsx
@@ -938,7 +938,7 @@
         <v>137092470</v>
       </c>
       <c r="B4" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>137092472</v>
       </c>
       <c r="B5" t="n">
-        <v>99447</v>
+        <v>99453</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>137092473</v>
       </c>
       <c r="B6" t="n">
-        <v>108451</v>
+        <v>108457</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>137092474</v>
       </c>
       <c r="B7" t="n">
-        <v>108451</v>
+        <v>108457</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>137092475</v>
       </c>
       <c r="B8" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>137092468</v>
       </c>
       <c r="B9" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>137092471</v>
       </c>
       <c r="B10" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 55975-2025 artfynd.xlsx
+++ b/artfynd/A 55975-2025 artfynd.xlsx
@@ -1162,7 +1162,7 @@
         <v>137092473</v>
       </c>
       <c r="B6" t="n">
-        <v>108457</v>
+        <v>108458</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>137092474</v>
       </c>
       <c r="B7" t="n">
-        <v>108457</v>
+        <v>108458</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 55975-2025 artfynd.xlsx
+++ b/artfynd/A 55975-2025 artfynd.xlsx
@@ -938,7 +938,7 @@
         <v>137092470</v>
       </c>
       <c r="B4" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>137092472</v>
       </c>
       <c r="B5" t="n">
-        <v>99453</v>
+        <v>99465</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>137092473</v>
       </c>
       <c r="B6" t="n">
-        <v>108458</v>
+        <v>108470</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>137092474</v>
       </c>
       <c r="B7" t="n">
-        <v>108458</v>
+        <v>108470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>137092475</v>
       </c>
       <c r="B8" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>137092468</v>
       </c>
       <c r="B9" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>137092471</v>
       </c>
       <c r="B10" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 55975-2025 artfynd.xlsx
+++ b/artfynd/A 55975-2025 artfynd.xlsx
@@ -938,7 +938,7 @@
         <v>137092470</v>
       </c>
       <c r="B4" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>137092472</v>
       </c>
       <c r="B5" t="n">
-        <v>99465</v>
+        <v>99466</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>137092473</v>
       </c>
       <c r="B6" t="n">
-        <v>108470</v>
+        <v>108471</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>137092474</v>
       </c>
       <c r="B7" t="n">
-        <v>108470</v>
+        <v>108471</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>137092475</v>
       </c>
       <c r="B8" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>137092468</v>
       </c>
       <c r="B9" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>137092471</v>
       </c>
       <c r="B10" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 55975-2025 artfynd.xlsx
+++ b/artfynd/A 55975-2025 artfynd.xlsx
@@ -938,7 +938,7 @@
         <v>137092470</v>
       </c>
       <c r="B4" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>137092472</v>
       </c>
       <c r="B5" t="n">
-        <v>99466</v>
+        <v>99469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>137092473</v>
       </c>
       <c r="B6" t="n">
-        <v>108471</v>
+        <v>108474</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>137092474</v>
       </c>
       <c r="B7" t="n">
-        <v>108471</v>
+        <v>108474</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>137092475</v>
       </c>
       <c r="B8" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>137092468</v>
       </c>
       <c r="B9" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>137092471</v>
       </c>
       <c r="B10" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 55975-2025 artfynd.xlsx
+++ b/artfynd/A 55975-2025 artfynd.xlsx
@@ -938,7 +938,7 @@
         <v>137092470</v>
       </c>
       <c r="B4" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>137092472</v>
       </c>
       <c r="B5" t="n">
-        <v>99469</v>
+        <v>99473</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>137092473</v>
       </c>
       <c r="B6" t="n">
-        <v>108474</v>
+        <v>108480</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>137092474</v>
       </c>
       <c r="B7" t="n">
-        <v>108474</v>
+        <v>108480</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>137092475</v>
       </c>
       <c r="B8" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>137092468</v>
       </c>
       <c r="B9" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>137092471</v>
       </c>
       <c r="B10" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
